--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">ジュン</t>
   </si>
   <si>
-    <t xml:space="preserve">ムクバート</t>
+    <t xml:space="preserve">ムクバード</t>
   </si>
   <si>
     <t xml:space="preserve">ムクホーク</t>

--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -59247,7 +59247,7 @@
         <v>1063</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="30" t="s">
@@ -59268,7 +59268,7 @@
         <v>1066</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="30" t="s">

--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -59335,7 +59335,7 @@
         <v>1076</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>1073</v>

--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -57562,7 +57562,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -58745,6 +58745,81 @@
         <v>1000</v>
       </c>
       <c r="G58" s="30" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>南の孤島</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="E59" s="30"/>
+      <c r="F59" s="52" t="inlineStr">
+        <is>
+          <t>謎のチケット・不思議なチケットで渡る（ラティオス・ラティアス）</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>やけたとう</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="E60" s="30"/>
+      <c r="F60" s="52" t="inlineStr">
+        <is>
+          <t>謎のチケット・不思議なチケットで渡る（ライコウ・スイクン・エンテイ）</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>ナナシマ</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="E61" s="30"/>
+      <c r="F61" s="52" t="inlineStr">
+        <is>
+          <t>謎のチケットで渡る（ファイヤー・サンダー・フリーザー）</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="s">
         <v>947</v>
       </c>
     </row>

--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -6803,7 +6803,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.63"/>
@@ -8454,6 +8454,38 @@
         <v>2500</v>
       </c>
       <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>ひでんマシン なみのり</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>覚えると 海上マスに入れるようになる（袋には入らない。すてる・とられることもない）</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>サファリゾーンのイベントでもらう（仕様書4.1.2の案）。イベントマスの効果の型「アイテム」で わたす</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
         <is>
           <t>×</t>
         </is>

--- a/ポケモンゲームデータ_v34.xlsx
+++ b/ポケモンゲームデータ_v34.xlsx
@@ -8566,7 +8566,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" s="30"/>
     </row>
@@ -8590,7 +8590,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -8614,7 +8614,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4" s="30"/>
     </row>
@@ -8638,7 +8638,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" s="30"/>
     </row>
@@ -8662,7 +8662,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H6" s="30"/>
     </row>
@@ -8686,7 +8686,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7" s="30"/>
     </row>
@@ -8710,7 +8710,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H8" s="30"/>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H9" s="30"/>
     </row>
@@ -8758,7 +8758,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" s="30"/>
     </row>
@@ -8782,7 +8782,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H11" s="30"/>
     </row>
@@ -8806,7 +8806,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H12" s="30"/>
     </row>
@@ -8830,7 +8830,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="30"/>
     </row>
@@ -8854,7 +8854,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="30"/>
     </row>
@@ -8878,7 +8878,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H15" s="30"/>
     </row>
@@ -8902,7 +8902,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="30"/>
     </row>
@@ -8926,7 +8926,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="30"/>
     </row>
@@ -8950,7 +8950,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="30"/>
     </row>
@@ -8974,7 +8974,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" s="30"/>
     </row>
@@ -8998,7 +8998,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="30"/>
     </row>
@@ -9022,7 +9022,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="30"/>
     </row>
@@ -9046,7 +9046,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="30"/>
     </row>
@@ -9070,7 +9070,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="30"/>
     </row>
@@ -9094,7 +9094,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H24" s="30"/>
     </row>
@@ -9118,7 +9118,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="30"/>
     </row>
@@ -9142,7 +9142,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="30"/>
     </row>
@@ -9190,7 +9190,7 @@
         <v>34</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H28" s="30"/>
     </row>
@@ -9214,7 +9214,7 @@
         <v>34</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H29" s="30"/>
     </row>
@@ -9238,7 +9238,7 @@
         <v>34</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H30" s="30"/>
     </row>
@@ -9262,7 +9262,7 @@
         <v>34</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H31" s="30"/>
     </row>
@@ -9286,7 +9286,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" s="30"/>
     </row>
@@ -9310,7 +9310,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H33" s="30"/>
     </row>
@@ -9334,7 +9334,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H34" s="30"/>
     </row>
@@ -9358,7 +9358,7 @@
         <v>8</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H35" s="30"/>
     </row>
@@ -9382,7 +9382,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H36" s="30"/>
     </row>
@@ -9406,7 +9406,7 @@
         <v>8</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H37" s="30"/>
     </row>
@@ -9430,7 +9430,7 @@
         <v>8</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H38" s="30"/>
     </row>
@@ -9454,7 +9454,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H39" s="30" t="s">
         <v>1317</v>
@@ -9480,7 +9480,7 @@
         <v>8</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H40" s="30"/>
     </row>
@@ -9504,7 +9504,7 @@
         <v>8</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H41" s="30" t="s">
         <v>1318</v>
@@ -9530,7 +9530,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H42" s="30"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>8</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H43" s="30"/>
     </row>
@@ -9578,7 +9578,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H44" s="30"/>
     </row>
@@ -9602,7 +9602,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" s="30"/>
     </row>
@@ -9626,7 +9626,7 @@
         <v>8</v>
       </c>
       <c r="G46" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H46" s="30"/>
     </row>
@@ -9650,7 +9650,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" s="30"/>
     </row>
@@ -9674,7 +9674,7 @@
         <v>8</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" s="30"/>
     </row>
@@ -9698,7 +9698,7 @@
         <v>8</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" s="30"/>
     </row>
@@ -9722,7 +9722,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H50" s="30"/>
     </row>
@@ -9746,7 +9746,7 @@
         <v>8</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H51" s="30"/>
     </row>
@@ -9770,7 +9770,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H52" s="30"/>
     </row>
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H53" s="30"/>
     </row>
@@ -9818,7 +9818,7 @@
         <v>8</v>
       </c>
       <c r="G54" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H54" s="30" t="s">
         <v>1317</v>
@@ -9844,7 +9844,7 @@
         <v>8</v>
       </c>
       <c r="G55" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H55" s="30"/>
     </row>
@@ -9868,7 +9868,7 @@
         <v>8</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H56" s="30" t="s">
         <v>1318</v>
@@ -9894,7 +9894,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H57" s="30"/>
     </row>
@@ -9918,7 +9918,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H58" s="30"/>
     </row>
@@ -9942,7 +9942,7 @@
         <v>8</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H59" s="30"/>
     </row>
@@ -9966,7 +9966,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H60" s="30"/>
     </row>
@@ -9990,7 +9990,7 @@
         <v>8</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H61" s="30"/>
     </row>
@@ -10014,7 +10014,7 @@
         <v>8</v>
       </c>
       <c r="G62" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H62" s="30"/>
     </row>
@@ -10038,7 +10038,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H63" s="30"/>
     </row>
@@ -10062,7 +10062,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H64" s="30"/>
     </row>
@@ -10086,7 +10086,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H65" s="30"/>
     </row>
@@ -10110,7 +10110,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H66" s="30"/>
     </row>
@@ -10134,7 +10134,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H67" s="30"/>
     </row>
@@ -10158,7 +10158,7 @@
         <v>8</v>
       </c>
       <c r="G68" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H68" s="30"/>
     </row>
@@ -10206,7 +10206,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H70" s="30"/>
     </row>
@@ -10230,7 +10230,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H71" s="30"/>
     </row>
@@ -10254,7 +10254,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H72" s="30"/>
     </row>
@@ -10278,7 +10278,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H73" s="30"/>
     </row>
@@ -10302,7 +10302,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H74" s="30"/>
     </row>
@@ -10326,7 +10326,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H75" s="30"/>
     </row>
@@ -10350,7 +10350,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H76" s="30"/>
     </row>
@@ -10374,7 +10374,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H77" s="30"/>
     </row>
@@ -10398,7 +10398,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H78" s="30"/>
     </row>
@@ -10446,7 +10446,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H80" s="30"/>
     </row>
@@ -10470,7 +10470,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H81" s="30"/>
     </row>
@@ -10494,7 +10494,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H82" s="30"/>
     </row>
@@ -10518,7 +10518,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H83" s="30"/>
     </row>
@@ -10542,7 +10542,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H84" s="30"/>
     </row>
@@ -10566,7 +10566,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H85" s="30"/>
     </row>
@@ -10590,7 +10590,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H86" s="30" t="s">
         <v>1318</v>
@@ -10616,7 +10616,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H87" s="30"/>
     </row>
@@ -10640,7 +10640,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H88" s="30"/>
     </row>
@@ -10664,7 +10664,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H89" s="30"/>
     </row>
@@ -10688,7 +10688,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H90" s="30"/>
     </row>
@@ -10712,7 +10712,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H91" s="30"/>
     </row>
@@ -10736,7 +10736,7 @@
         <v>13</v>
       </c>
       <c r="G92" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H92" s="30"/>
     </row>
@@ -10760,7 +10760,7 @@
         <v>13</v>
       </c>
       <c r="G93" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H93" s="30"/>
     </row>
@@ -10784,7 +10784,7 @@
         <v>13</v>
       </c>
       <c r="G94" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H94" s="30"/>
     </row>
@@ -10808,7 +10808,7 @@
         <v>13</v>
       </c>
       <c r="G95" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H95" s="30"/>
     </row>
@@ -10832,7 +10832,7 @@
         <v>13</v>
       </c>
       <c r="G96" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H96" s="30"/>
     </row>
@@ -10856,7 +10856,7 @@
         <v>13</v>
       </c>
       <c r="G97" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H97" s="30"/>
     </row>
@@ -10880,7 +10880,7 @@
         <v>13</v>
       </c>
       <c r="G98" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H98" s="30"/>
     </row>
@@ -10904,7 +10904,7 @@
         <v>13</v>
       </c>
       <c r="G99" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H99" s="30"/>
     </row>
@@ -10928,7 +10928,7 @@
         <v>13</v>
       </c>
       <c r="G100" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H100" s="30"/>
     </row>
@@ -10952,7 +10952,7 @@
         <v>13</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H101" s="30"/>
     </row>
@@ -10976,7 +10976,7 @@
         <v>13</v>
       </c>
       <c r="G102" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H102" s="30"/>
     </row>
@@ -11000,7 +11000,7 @@
         <v>13</v>
       </c>
       <c r="G103" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H103" s="30"/>
     </row>
@@ -11024,7 +11024,7 @@
         <v>13</v>
       </c>
       <c r="G104" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H104" s="30" t="s">
         <v>1317</v>
@@ -11050,7 +11050,7 @@
         <v>13</v>
       </c>
       <c r="G105" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H105" s="30"/>
     </row>
@@ -11074,7 +11074,7 @@
         <v>13</v>
       </c>
       <c r="G106" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H106" s="30"/>
     </row>
@@ -11098,7 +11098,7 @@
         <v>13</v>
       </c>
       <c r="G107" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H107" s="30" t="s">
         <v>1318</v>
@@ -11148,7 +11148,7 @@
         <v>13</v>
       </c>
       <c r="G109" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H109" s="30" t="s">
         <v>1318</v>
@@ -11174,7 +11174,7 @@
         <v>13</v>
       </c>
       <c r="G110" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H110" s="30"/>
     </row>
@@ -11198,7 +11198,7 @@
         <v>13</v>
       </c>
       <c r="G111" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H111" s="30"/>
     </row>
@@ -11222,7 +11222,7 @@
         <v>13</v>
       </c>
       <c r="G112" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H112" s="30" t="s">
         <v>1317</v>
@@ -11248,7 +11248,7 @@
         <v>13</v>
       </c>
       <c r="G113" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H113" s="30"/>
     </row>
@@ -11272,7 +11272,7 @@
         <v>13</v>
       </c>
       <c r="G114" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H114" s="30" t="s">
         <v>1317</v>
@@ -11298,7 +11298,7 @@
         <v>13</v>
       </c>
       <c r="G115" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H115" s="30" t="s">
         <v>1318</v>
@@ -11324,7 +11324,7 @@
         <v>13</v>
       </c>
       <c r="G116" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H116" s="30"/>
     </row>
@@ -11348,7 +11348,7 @@
         <v>13</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H117" s="30"/>
     </row>
@@ -11372,7 +11372,7 @@
         <v>13</v>
       </c>
       <c r="G118" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H118" s="30"/>
     </row>
@@ -11396,7 +11396,7 @@
         <v>13</v>
       </c>
       <c r="G119" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H119" s="30" t="s">
         <v>1317</v>
@@ -11422,7 +11422,7 @@
         <v>13</v>
       </c>
       <c r="G120" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H120" s="30" t="s">
         <v>1317</v>
@@ -11448,7 +11448,7 @@
         <v>13</v>
       </c>
       <c r="G121" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H121" s="30" t="s">
         <v>1318</v>
@@ -11474,7 +11474,7 @@
         <v>13</v>
       </c>
       <c r="G122" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H122" s="30" t="s">
         <v>1318</v>
@@ -11500,7 +11500,7 @@
         <v>13</v>
       </c>
       <c r="G123" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H123" s="30"/>
     </row>
@@ -11524,7 +11524,7 @@
         <v>13</v>
       </c>
       <c r="G124" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H124" s="30" t="s">
         <v>1318</v>
@@ -11550,7 +11550,7 @@
         <v>13</v>
       </c>
       <c r="G125" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H125" s="30" t="s">
         <v>1317</v>
@@ -11576,7 +11576,7 @@
         <v>13</v>
       </c>
       <c r="G126" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H126" s="30"/>
     </row>
@@ -11600,7 +11600,7 @@
         <v>13</v>
       </c>
       <c r="G127" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H127" s="30"/>
     </row>
@@ -11624,7 +11624,7 @@
         <v>13</v>
       </c>
       <c r="G128" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H128" s="30"/>
     </row>
@@ -11648,7 +11648,7 @@
         <v>13</v>
       </c>
       <c r="G129" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H129" s="30"/>
     </row>
@@ -11694,7 +11694,7 @@
         <v>13</v>
       </c>
       <c r="G131" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H131" s="30"/>
     </row>
@@ -11718,7 +11718,7 @@
         <v>13</v>
       </c>
       <c r="G132" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H132" s="30"/>
     </row>
@@ -11742,7 +11742,7 @@
         <v>13</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H133" s="30" t="s">
         <v>1318</v>
@@ -11768,7 +11768,7 @@
         <v>13</v>
       </c>
       <c r="G134" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H134" s="30" t="s">
         <v>1317</v>
@@ -11794,7 +11794,7 @@
         <v>13</v>
       </c>
       <c r="G135" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H135" s="30"/>
     </row>
@@ -11818,7 +11818,7 @@
         <v>13</v>
       </c>
       <c r="G136" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H136" s="30"/>
     </row>
@@ -11842,7 +11842,7 @@
         <v>13</v>
       </c>
       <c r="G137" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H137" s="30"/>
     </row>
@@ -11866,7 +11866,7 @@
         <v>13</v>
       </c>
       <c r="G138" s="30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H138" s="30"/>
     </row>
@@ -11890,7 +11890,7 @@
         <v>22</v>
       </c>
       <c r="G139" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H139" s="30"/>
     </row>
@@ -11914,7 +11914,7 @@
         <v>22</v>
       </c>
       <c r="G140" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H140" s="30"/>
     </row>
@@ -11938,7 +11938,7 @@
         <v>22</v>
       </c>
       <c r="G141" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H141" s="30"/>
     </row>
@@ -11962,7 +11962,7 @@
         <v>22</v>
       </c>
       <c r="G142" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H142" s="30" t="s">
         <v>1318</v>
@@ -11988,7 +11988,7 @@
         <v>22</v>
       </c>
       <c r="G143" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H143" s="30"/>
     </row>
@@ -12012,7 +12012,7 @@
         <v>22</v>
       </c>
       <c r="G144" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H144" s="30" t="s">
         <v>1317</v>
@@ -12038,7 +12038,7 @@
         <v>22</v>
       </c>
       <c r="G145" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H145" s="30"/>
     </row>
@@ -12062,7 +12062,7 @@
         <v>22</v>
       </c>
       <c r="G146" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H146" s="30"/>
     </row>
@@ -12086,7 +12086,7 @@
         <v>22</v>
       </c>
       <c r="G147" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H147" s="30"/>
     </row>
@@ -12110,7 +12110,7 @@
         <v>22</v>
       </c>
       <c r="G148" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H148" s="30" t="s">
         <v>1317</v>
@@ -12136,7 +12136,7 @@
         <v>22</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H149" s="30"/>
     </row>
@@ -12160,7 +12160,7 @@
         <v>22</v>
       </c>
       <c r="G150" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H150" s="30"/>
     </row>
@@ -12184,7 +12184,7 @@
         <v>22</v>
       </c>
       <c r="G151" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H151" s="30"/>
     </row>
@@ -12208,7 +12208,7 @@
         <v>22</v>
       </c>
       <c r="G152" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H152" s="30" t="s">
         <v>1318</v>
@@ -12234,7 +12234,7 @@
         <v>22</v>
       </c>
       <c r="G153" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H153" s="30"/>
     </row>
@@ -12258,7 +12258,7 @@
         <v>22</v>
       </c>
       <c r="G154" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H154" s="30"/>
     </row>
@@ -12282,7 +12282,7 @@
         <v>22</v>
       </c>
       <c r="G155" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H155" s="30"/>
     </row>
@@ -12306,7 +12306,7 @@
         <v>22</v>
       </c>
       <c r="G156" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H156" s="30" t="s">
         <v>1318</v>
@@ -12332,7 +12332,7 @@
         <v>22</v>
       </c>
       <c r="G157" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H157" s="30" t="s">
         <v>1317</v>
@@ -12358,7 +12358,7 @@
         <v>22</v>
       </c>
       <c r="G158" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H158" s="30"/>
     </row>
@@ -12382,7 +12382,7 @@
         <v>22</v>
       </c>
       <c r="G159" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H159" s="30"/>
     </row>
@@ -12406,7 +12406,7 @@
         <v>22</v>
       </c>
       <c r="G160" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H160" s="30"/>
     </row>
@@ -12430,7 +12430,7 @@
         <v>22</v>
       </c>
       <c r="G161" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H161" s="30"/>
     </row>
@@ -12476,7 +12476,7 @@
         <v>22</v>
       </c>
       <c r="G163" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H163" s="30"/>
     </row>
@@ -12500,7 +12500,7 @@
         <v>22</v>
       </c>
       <c r="G164" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H164" s="30"/>
     </row>
@@ -12524,7 +12524,7 @@
         <v>22</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H165" s="30"/>
     </row>
@@ -12548,7 +12548,7 @@
         <v>22</v>
       </c>
       <c r="G166" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H166" s="30"/>
     </row>
@@ -12572,7 +12572,7 @@
         <v>22</v>
       </c>
       <c r="G167" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H167" s="30"/>
     </row>
@@ -12596,7 +12596,7 @@
         <v>22</v>
       </c>
       <c r="G168" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H168" s="30"/>
     </row>
@@ -12620,7 +12620,7 @@
         <v>22</v>
       </c>
       <c r="G169" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H169" s="30"/>
     </row>
@@ -12644,7 +12644,7 @@
         <v>22</v>
       </c>
       <c r="G170" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H170" s="30"/>
     </row>
@@ -12668,7 +12668,7 @@
         <v>22</v>
       </c>
       <c r="G171" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H171" s="30"/>
     </row>
@@ -12692,7 +12692,7 @@
         <v>22</v>
       </c>
       <c r="G172" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H172" s="30"/>
     </row>
@@ -12716,7 +12716,7 @@
         <v>22</v>
       </c>
       <c r="G173" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H173" s="30"/>
     </row>
@@ -12740,7 +12740,7 @@
         <v>22</v>
       </c>
       <c r="G174" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H174" s="30"/>
     </row>
@@ -12764,7 +12764,7 @@
         <v>22</v>
       </c>
       <c r="G175" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H175" s="30"/>
     </row>
@@ -12788,7 +12788,7 @@
         <v>22</v>
       </c>
       <c r="G176" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H176" s="30"/>
     </row>
@@ -12812,7 +12812,7 @@
         <v>22</v>
       </c>
       <c r="G177" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H177" s="30"/>
     </row>
@@ -12836,7 +12836,7 @@
         <v>22</v>
       </c>
       <c r="G178" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H178" s="30"/>
     </row>
@@ -12860,7 +12860,7 @@
         <v>22</v>
       </c>
       <c r="G179" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H179" s="30"/>
     </row>
@@ -12884,7 +12884,7 @@
         <v>22</v>
       </c>
       <c r="G180" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H180" s="30"/>
     </row>
@@ -12908,7 +12908,7 @@
         <v>22</v>
       </c>
       <c r="G181" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H181" s="30"/>
     </row>
@@ -12932,7 +12932,7 @@
         <v>22</v>
       </c>
       <c r="G182" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H182" s="30"/>
     </row>
@@ -12956,7 +12956,7 @@
         <v>22</v>
       </c>
       <c r="G183" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H183" s="30"/>
     </row>
@@ -12980,7 +12980,7 @@
         <v>22</v>
       </c>
       <c r="G184" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H184" s="30"/>
     </row>
@@ -13004,7 +13004,7 @@
         <v>22</v>
       </c>
       <c r="G185" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H185" s="30"/>
     </row>
@@ -13028,7 +13028,7 @@
         <v>22</v>
       </c>
       <c r="G186" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H186" s="30"/>
     </row>
@@ -13052,7 +13052,7 @@
         <v>22</v>
       </c>
       <c r="G187" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H187" s="30"/>
     </row>
@@ -13076,7 +13076,7 @@
         <v>22</v>
       </c>
       <c r="G188" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H188" s="30"/>
     </row>
@@ -13100,7 +13100,7 @@
         <v>22</v>
       </c>
       <c r="G189" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H189" s="30"/>
     </row>
@@ -13124,7 +13124,7 @@
         <v>22</v>
       </c>
       <c r="G190" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H190" s="30"/>
     </row>
@@ -13148,7 +13148,7 @@
         <v>22</v>
       </c>
       <c r="G191" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H191" s="30"/>
     </row>
@@ -13172,7 +13172,7 @@
         <v>22</v>
       </c>
       <c r="G192" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H192" s="30"/>
     </row>
@@ -13196,7 +13196,7 @@
         <v>22</v>
       </c>
       <c r="G193" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H193" s="30"/>
     </row>
@@ -13220,7 +13220,7 @@
         <v>22</v>
       </c>
       <c r="G194" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H194" s="30"/>
     </row>
@@ -13244,7 +13244,7 @@
         <v>22</v>
       </c>
       <c r="G195" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H195" s="30"/>
     </row>
@@ -13268,7 +13268,7 @@
         <v>22</v>
       </c>
       <c r="G196" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H196" s="30"/>
     </row>
@@ -13292,7 +13292,7 @@
         <v>22</v>
       </c>
       <c r="G197" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H197" s="30"/>
     </row>
@@ -13340,7 +13340,7 @@
         <v>22</v>
       </c>
       <c r="G199" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H199" s="30"/>
     </row>
@@ -13364,7 +13364,7 @@
         <v>22</v>
       </c>
       <c r="G200" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H200" s="30"/>
     </row>
@@ -13388,7 +13388,7 @@
         <v>22</v>
       </c>
       <c r="G201" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H201" s="30"/>
     </row>
@@ -13412,7 +13412,7 @@
         <v>22</v>
       </c>
       <c r="G202" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H202" s="30"/>
     </row>
@@ -13436,7 +13436,7 @@
         <v>22</v>
       </c>
       <c r="G203" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H203" s="30"/>
     </row>
@@ -13460,7 +13460,7 @@
         <v>22</v>
       </c>
       <c r="G204" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H204" s="30"/>
     </row>
@@ -13484,7 +13484,7 @@
         <v>22</v>
       </c>
       <c r="G205" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H205" s="30"/>
     </row>
@@ -13508,7 +13508,7 @@
         <v>22</v>
       </c>
       <c r="G206" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H206" s="30"/>
     </row>
@@ -13532,7 +13532,7 @@
         <v>22</v>
       </c>
       <c r="G207" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H207" s="30"/>
     </row>
@@ -13556,7 +13556,7 @@
         <v>22</v>
       </c>
       <c r="G208" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H208" s="30"/>
     </row>
@@ -13580,7 +13580,7 @@
         <v>22</v>
       </c>
       <c r="G209" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H209" s="30"/>
     </row>
@@ -13604,7 +13604,7 @@
         <v>22</v>
       </c>
       <c r="G210" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H210" s="30"/>
     </row>
@@ -13628,7 +13628,7 @@
         <v>22</v>
       </c>
       <c r="G211" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H211" s="30"/>
     </row>
@@ -13652,7 +13652,7 @@
         <v>22</v>
       </c>
       <c r="G212" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H212" s="30"/>
     </row>
@@ -13676,7 +13676,7 @@
         <v>22</v>
       </c>
       <c r="G213" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H213" s="30"/>
     </row>
@@ -13700,7 +13700,7 @@
         <v>22</v>
       </c>
       <c r="G214" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H214" s="30"/>
     </row>
@@ -13724,7 +13724,7 @@
         <v>22</v>
       </c>
       <c r="G215" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H215" s="30"/>
     </row>
@@ -13748,7 +13748,7 @@
         <v>22</v>
       </c>
       <c r="G216" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H216" s="30"/>
     </row>
@@ -13772,7 +13772,7 @@
         <v>22</v>
       </c>
       <c r="G217" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H217" s="30"/>
     </row>
@@ -13796,7 +13796,7 @@
         <v>22</v>
       </c>
       <c r="G218" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H218" s="30"/>
     </row>
@@ -13820,7 +13820,7 @@
         <v>22</v>
       </c>
       <c r="G219" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H219" s="30"/>
     </row>
@@ -13844,7 +13844,7 @@
         <v>22</v>
       </c>
       <c r="G220" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H220" s="30"/>
     </row>
@@ -13868,7 +13868,7 @@
         <v>22</v>
       </c>
       <c r="G221" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H221" s="30" t="s">
         <v>1317</v>
@@ -13894,7 +13894,7 @@
         <v>22</v>
       </c>
       <c r="G222" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H222" s="30" t="s">
         <v>1318</v>
@@ -13920,7 +13920,7 @@
         <v>22</v>
       </c>
       <c r="G223" s="30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H223" s="30"/>
     </row>
@@ -13944,7 +13944,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H224" s="30"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H225" s="30"/>
     </row>
@@ -13992,7 +13992,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H226" s="30"/>
     </row>
@@ -14016,7 +14016,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H227" s="30"/>
     </row>
@@ -14040,7 +14040,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H228" s="30" t="s">
         <v>1317</v>
@@ -14066,7 +14066,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H229" s="30"/>
     </row>
@@ -14090,7 +14090,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H230" s="30"/>
     </row>
@@ -14114,7 +14114,7 @@
         <v>25</v>
       </c>
       <c r="G231" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H231" s="30"/>
     </row>
@@ -14138,7 +14138,7 @@
         <v>25</v>
       </c>
       <c r="G232" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H232" s="30"/>
     </row>
@@ -14162,7 +14162,7 @@
         <v>25</v>
       </c>
       <c r="G233" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H233" s="30"/>
     </row>
@@ -14186,7 +14186,7 @@
         <v>25</v>
       </c>
       <c r="G234" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H234" s="30"/>
     </row>
@@ -14210,7 +14210,7 @@
         <v>25</v>
       </c>
       <c r="G235" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H235" s="30"/>
     </row>
@@ -14234,7 +14234,7 @@
         <v>25</v>
       </c>
       <c r="G236" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H236" s="30"/>
     </row>
@@ -14258,7 +14258,7 @@
         <v>25</v>
       </c>
       <c r="G237" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H237" s="30"/>
     </row>
@@ -14282,7 +14282,7 @@
         <v>25</v>
       </c>
       <c r="G238" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H238" s="30"/>
     </row>
@@ -14306,7 +14306,7 @@
         <v>25</v>
       </c>
       <c r="G239" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H239" s="30"/>
     </row>
@@ -14330,7 +14330,7 @@
         <v>25</v>
       </c>
       <c r="G240" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H240" s="30"/>
     </row>
@@ -14354,7 +14354,7 @@
         <v>25</v>
       </c>
       <c r="G241" s="30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H241" s="30"/>
     </row>
